--- a/data/trans_bre/P6903-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 21,54</t>
+          <t>-32,02; 20,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 36,99</t>
+          <t>-47,91; 39,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 44,31</t>
+          <t>-30,36; 45,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 58,13</t>
+          <t>-62,52; 61,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 79,51</t>
+          <t>-68,81; 74,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,16; 236,29</t>
+          <t>-80,76; 225,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 169,03</t>
+          <t>-54,52; 193,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-91,82; —</t>
+          <t>-83,59; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 5,63</t>
+          <t>-20,24; 4,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 24,24</t>
+          <t>-6,24; 25,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 13,96</t>
+          <t>-23,03; 13,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 20,37</t>
+          <t>-23,93; 20,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,07; 20,3</t>
+          <t>-51,62; 16,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 131,99</t>
+          <t>-21,07; 133,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,7; 48,02</t>
+          <t>-52,68; 42,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 71,83</t>
+          <t>-44,24; 75,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 9,89</t>
+          <t>-17,59; 9,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 23,58</t>
+          <t>-6,03; 24,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 21,46</t>
+          <t>-7,55; 21,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 23,12</t>
+          <t>-3,44; 23,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 34,62</t>
+          <t>-44,44; 30,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 105,58</t>
+          <t>-16,84; 112,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 70,86</t>
+          <t>-18,58; 70,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 111,18</t>
+          <t>-14,77; 112,1</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 29,66</t>
+          <t>-4,33; 30,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 23,41</t>
+          <t>-11,43; 19,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 18,09</t>
+          <t>-15,07; 19,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 14,95</t>
+          <t>-22,37; 14,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 140,96</t>
+          <t>-14,46; 145,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 166,22</t>
+          <t>-49,34; 133,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 57,04</t>
+          <t>-32,62; 62,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,33; 44,69</t>
+          <t>-52,17; 42,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 45,69</t>
+          <t>-10,16; 44,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,8</t>
+          <t>7,52; 53,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 24,68</t>
+          <t>-24,3; 24,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 25,81</t>
+          <t>-3,75; 25,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 413,49</t>
+          <t>-54,63; 472,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,55; 1012,62</t>
+          <t>19,43; 1049,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 73,36</t>
+          <t>-46,26; 73,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 106,11</t>
+          <t>-9,24; 103,48</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,89</t>
+          <t>0,0; 80,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,23</t>
+          <t>-8,31; 6,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 18,66</t>
+          <t>2,58; 18,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 12,36</t>
+          <t>-6,82; 10,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 12,81</t>
+          <t>-7,46; 13,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 30,33</t>
+          <t>-24,54; 22,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 90,77</t>
+          <t>9,93; 90,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 35,28</t>
+          <t>-16,05; 30,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 41,7</t>
+          <t>-19,01; 43,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6903-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,73</t>
+          <t>-11,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>-21,27%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 20,28</t>
+          <t>-29,79; 16,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-47,91; 39,93</t>
+          <t>-44,49; 46,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 45,93</t>
+          <t>-28,45; 44,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 61,69</t>
+          <t>-66,18; 51,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,81; 74,8</t>
+          <t>-67,84; 66,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 225,39</t>
+          <t>-76,25; 363,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 193,42</t>
+          <t>-54,44; 195,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-83,59; —</t>
+          <t>-83,15; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-4,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,09%</t>
+          <t>-10,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 4,85</t>
+          <t>-20,22; 5,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 25,36</t>
+          <t>-5,83; 25,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 13,01</t>
+          <t>-20,59; 13,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 20,93</t>
+          <t>-29,33; 17,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 16,94</t>
+          <t>-51,83; 19,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 133,96</t>
+          <t>-18,59; 146,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 42,17</t>
+          <t>-48,6; 48,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 75,5</t>
+          <t>-50,06; 52,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 9,59</t>
+          <t>-18,64; 8,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 24,9</t>
+          <t>-5,66; 23,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 21,74</t>
+          <t>-7,72; 21,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 23,68</t>
+          <t>-2,08; 23,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 30,85</t>
+          <t>-44,38; 29,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 112,72</t>
+          <t>-17,63; 113,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 70,53</t>
+          <t>-17,39; 71,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 112,1</t>
+          <t>-7,36; 114,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,39%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 30,26</t>
+          <t>-5,83; 30,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 19,59</t>
+          <t>-10,79; 23,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 19,17</t>
+          <t>-14,63; 19,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 14,5</t>
+          <t>-6,06; 16,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 145,11</t>
+          <t>-20,33; 138,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 133,96</t>
+          <t>-45,93; 176,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 62,43</t>
+          <t>-31,66; 58,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 42,92</t>
+          <t>-12,07; 55,81</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,03</t>
+          <t>11,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 44,44</t>
+          <t>-10,51; 44,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 53,33</t>
+          <t>7,09; 54,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 24,6</t>
+          <t>-24,06; 25,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 25,58</t>
+          <t>-3,02; 26,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 472,89</t>
+          <t>-63,35; 461,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 1049,87</t>
+          <t>9,04; 920,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,26; 73,76</t>
+          <t>-46,79; 79,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 103,48</t>
+          <t>-8,75; 103,77</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,09</t>
+          <t>34,15</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,91</t>
+          <t>0,0; 84,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,57</t>
+          <t>-8,59; 6,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,58; 18,79</t>
+          <t>2,07; 19,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 10,76</t>
+          <t>-6,24; 11,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 13,31</t>
+          <t>-1,68; 13,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 22,58</t>
+          <t>-25,27; 23,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 90,61</t>
+          <t>7,63; 94,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 30,3</t>
+          <t>-13,89; 33,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 43,48</t>
+          <t>-4,31; 42,85</t>
         </is>
       </c>
     </row>
